--- a/config/xlsx/card_collection.xlsx
+++ b/config/xlsx/card_collection.xlsx
@@ -652,377 +652,315 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="13.75" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="13.75" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="13.75" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="13.75" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="13.75" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="17" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="3" t="str">
-        <x:v>pack_id</x:v>
-      </x:c>
-      <x:c r="B1" s="3" t="str">
-        <x:v>collection_id</x:v>
-      </x:c>
-      <x:c r="C1" s="3" t="str">
-        <x:v>name</x:v>
-      </x:c>
-      <x:c r="D1" s="3" t="str">
-        <x:v>star</x:v>
-      </x:c>
-      <x:c r="E1" s="3" t="str">
-        <x:v>icon</x:v>
-      </x:c>
-      <x:c r="F1" s="3" t="str">
-        <x:v>card_count</x:v>
-      </x:c>
-      <x:c r="G1" s="3" t="str">
-        <x:v>normal_weights</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="26" customHeight="1">
-      <x:c r="A2" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="str">
-        <x:v>1星卡包</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="str"/>
-      <x:c r="F2" s="1" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="str">
-        <x:v>[55,28,12,4,1]</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="26" customHeight="1">
-      <x:c r="A3" s="1" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B3" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="1" t="str">
-        <x:v>2星卡包</x:v>
-      </x:c>
-      <x:c r="D3" s="1" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E3" s="1" t="str"/>
-      <x:c r="F3" s="1" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G3" s="1" t="str">
-        <x:v>[55,28,12,4,1]</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="26" customHeight="1">
-      <x:c r="A4" s="1" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B4" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="1" t="str">
-        <x:v>3星卡包</x:v>
-      </x:c>
-      <x:c r="D4" s="1" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E4" s="1" t="str"/>
-      <x:c r="F4" s="1" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G4" s="1" t="str">
-        <x:v>[55,28,12,4,1]</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="26" customHeight="1">
-      <x:c r="A5" s="1" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B5" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="1" t="str">
-        <x:v>4星卡包</x:v>
-      </x:c>
-      <x:c r="D5" s="1" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E5" s="1" t="str"/>
-      <x:c r="F5" s="1" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="1" t="str">
-        <x:v>[55,28,12,4,1]</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="26" customHeight="1">
-      <x:c r="A6" s="1" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B6" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="1" t="str">
-        <x:v>5星卡包</x:v>
-      </x:c>
-      <x:c r="D6" s="1" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E6" s="1" t="str"/>
-      <x:c r="F6" s="1" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G6" s="1" t="str">
-        <x:v>[55,28,12,4,1]</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="13.75" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="13.75" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="13.75" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="13.75" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="13.75" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="17" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="3" t="str">
+        <v>pack_id</v>
+      </c>
+      <c r="B1" s="3" t="str">
+        <v>collection_id</v>
+      </c>
+      <c r="C1" s="3" t="str">
+        <v>name</v>
+      </c>
+      <c r="D1" s="3" t="str">
+        <v>star</v>
+      </c>
+      <c r="E1" s="3" t="str">
+        <v>icon</v>
+      </c>
+      <c r="F1" s="3" t="str">
+        <v>card_count</v>
+      </c>
+      <c r="G1" s="3" t="str">
+        <v>normal_weights</v>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="str">
+        <v>1星卡包</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="str" s="1">
+        <v>res://assets/items/card_pack.svg</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" s="1" t="str">
+        <v>[55,28,12,4,1]</v>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="str">
+        <v>2星卡包</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="str" s="1">
+        <v>res://assets/items/card_pack.svg</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" s="1" t="str">
+        <v>[55,28,12,4,1]</v>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="str">
+        <v>3星卡包</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="str" s="1">
+        <v>res://assets/items/card_pack.svg</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" s="1" t="str">
+        <v>[55,28,12,4,1]</v>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="str">
+        <v>4星卡包</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="str" s="1">
+        <v>res://assets/items/card_pack.svg</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" s="1" t="str">
+        <v>[55,28,12,4,1]</v>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1" t="str">
+        <v>5星卡包</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="str" s="1">
+        <v>res://assets/items/card_pack.svg</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" s="1" t="str">
+        <v>[55,28,12,4,1]</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="13.75" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="13.75" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="13.75" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="13.75" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="13.75" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="3" t="str">
-        <x:v>collection_id</x:v>
-      </x:c>
-      <x:c r="B1" s="3" t="str">
-        <x:v>source_type</x:v>
-      </x:c>
-      <x:c r="C1" s="3" t="str">
-        <x:v>source_id</x:v>
-      </x:c>
-      <x:c r="D1" s="3" t="str">
-        <x:v>min_value</x:v>
-      </x:c>
-      <x:c r="E1" s="3" t="str">
-        <x:v>pack_id</x:v>
-      </x:c>
-      <x:c r="F1" s="3" t="str">
-        <x:v>count</x:v>
-      </x:c>
-      <x:c r="G1" s="3" t="str">
-        <x:v>enabled</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="26" customHeight="1">
-      <x:c r="A2" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="str">
-        <x:v>quest</x:v>
-      </x:c>
-      <x:c r="C2" s="1"/>
-      <x:c r="D2" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G2" s="5" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="26" customHeight="1">
-      <x:c r="A3" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B3" s="1" t="str">
-        <x:v>quest</x:v>
-      </x:c>
-      <x:c r="C3" s="1"/>
-      <x:c r="D3" s="1" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E3" s="1" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F3" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G3" s="5" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="26" customHeight="1">
-      <x:c r="A4" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B4" s="1" t="str">
-        <x:v>quest</x:v>
-      </x:c>
-      <x:c r="C4" s="1"/>
-      <x:c r="D4" s="1" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E4" s="1" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F4" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G4" s="5" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="26" customHeight="1">
-      <x:c r="A5" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B5" s="1" t="str">
-        <x:v>order</x:v>
-      </x:c>
-      <x:c r="C5" s="1"/>
-      <x:c r="D5" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E5" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F5" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G5" s="5" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="26" customHeight="1">
-      <x:c r="A6" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B6" s="1" t="str">
-        <x:v>order</x:v>
-      </x:c>
-      <x:c r="C6" s="1"/>
-      <x:c r="D6" s="1" t="n">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="E6" s="1" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F6" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G6" s="5" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="26" customHeight="1">
-      <x:c r="A7" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B7" s="1" t="str">
-        <x:v>order</x:v>
-      </x:c>
-      <x:c r="C7" s="1"/>
-      <x:c r="D7" s="1" t="n">
-        <x:v>600</x:v>
-      </x:c>
-      <x:c r="E7" s="1" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F7" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G7" s="5" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="26" customHeight="1">
-      <x:c r="A8" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B8" s="1" t="str">
-        <x:v>circulation</x:v>
-      </x:c>
-      <x:c r="C8" s="1"/>
-      <x:c r="D8" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E8" s="1" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F8" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G8" s="5" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="26" customHeight="1">
-      <x:c r="A9" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B9" s="1" t="str">
-        <x:v>circulation</x:v>
-      </x:c>
-      <x:c r="C9" s="1"/>
-      <x:c r="D9" s="1" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E9" s="1" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F9" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G9" s="5" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="26" customHeight="1">
-      <x:c r="A10" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B10" s="1" t="str">
-        <x:v>circulation</x:v>
-      </x:c>
-      <x:c r="C10" s="1"/>
-      <x:c r="D10" s="1" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E10" s="1" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F10" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G10" s="5" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="13.75" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="13.75" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="13.75" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="13.75" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="13.75" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="3" t="str">
+        <v>collection_id</v>
+      </c>
+      <c r="B1" s="3" t="str">
+        <v>source_type</v>
+      </c>
+      <c r="C1" s="3" t="str">
+        <v>source_id</v>
+      </c>
+      <c r="D1" s="3" t="str">
+        <v>min_value</v>
+      </c>
+      <c r="E1" s="3" t="str">
+        <v>pack_id</v>
+      </c>
+      <c r="F1" s="3" t="str">
+        <v>count</v>
+      </c>
+      <c r="G1" s="3" t="str">
+        <v>enabled</v>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" t="n" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str" s="1">
+        <v>order</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" t="n" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n" s="1">
+        <v>1</v>
+      </c>
+      <c r="G2" t="b" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" t="n" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" t="str" s="1">
+        <v>order</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" t="n" s="1">
+        <v>200</v>
+      </c>
+      <c r="E3" t="n" s="1">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n" s="1">
+        <v>1</v>
+      </c>
+      <c r="G3" t="b" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" t="n" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" t="str" s="1">
+        <v>order</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" t="n" s="1">
+        <v>600</v>
+      </c>
+      <c r="E4" t="n" s="1">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n" s="1">
+        <v>1</v>
+      </c>
+      <c r="G4" t="b" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="5"/>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="5"/>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="5"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="5"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="5"/>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>